--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1157,238 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130066633</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norra udde, Norra udde, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565421</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6438293</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130066295</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norra udde, Norra udde, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>565470</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6438416</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130066295</v>
+        <v>130066539</v>
       </c>
       <c r="B7" t="n">
         <v>57898</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>130066539</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>130066633</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>130066539</v>
       </c>
       <c r="B7" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,6 +1389,115 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130092760</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norra udden A 53846, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565416</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6438318</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>130092760</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>130092760</v>
       </c>
       <c r="B8" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>130092760</v>
       </c>
       <c r="B8" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>130092760</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
         <v>130092760</v>
       </c>
       <c r="B8" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53846-2025 artfynd.xlsx
+++ b/artfynd/A 53846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7120925</v>
+        <v>7120757</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565384.7578147044</v>
+        <v>565385</v>
       </c>
       <c r="R2" t="n">
-        <v>6438306.764968686</v>
+        <v>6438307</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,14 @@
           <t>2011-12-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-12-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;33023</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;33024</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7120757</v>
+        <v>130066213</v>
       </c>
       <c r="B3" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,50 +792,55 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mosshult, Sm</t>
+          <t>Norra udde, Norra udde, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565384.7578147044</v>
+        <v>565477</v>
       </c>
       <c r="R3" t="n">
-        <v>6438306.764968686</v>
+        <v>6438442</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Östergötland</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Västervik</t>
+          <t>Åtvidaberg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -865,32 +850,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Dalhem</t>
+          <t>Gärdserum</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;33024</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,54 +885,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7119424</v>
+        <v>7120925</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565384.7578147044</v>
+        <v>565385</v>
       </c>
       <c r="R4" t="n">
-        <v>6438306.764968686</v>
+        <v>6438307</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,24 +969,14 @@
           <t>2011-12-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-12-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Mille Fagerström  ID;33022</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;33023</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,42 +1003,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7120097</v>
+        <v>7119424</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565384.7578147044</v>
+        <v>565385</v>
       </c>
       <c r="R5" t="n">
-        <v>6438306.764968686</v>
+        <v>6438307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,24 +1075,14 @@
           <t>2011-12-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-12-28</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;33025</t>
+          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Mille Fagerström  ID;33022</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,11 +1112,11 @@
         <v>130066633</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1278,7 +1228,7 @@
         <v>130066539</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1344,7 @@
         <v>130092760</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,6 +1447,112 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7120097</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mosshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>565385</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6438307</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2011-12-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2011-12-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;33025</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
